--- a/plugins/xiaohongshu-reimbursement-workflow/skills/xiaohongshu-reimbursement-workflow/assets/templates/xiaohongshu/supplement-detail.xlsx
+++ b/plugins/xiaohongshu-reimbursement-workflow/skills/xiaohongshu-reimbursement-workflow/assets/templates/xiaohongshu/supplement-detail.xlsx
@@ -9,9 +9,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
+    <x:numFmt numFmtId="210" formatCode="0"/>
+    <x:numFmt numFmtId="211" formatCode="0.0"/>
+    <x:numFmt numFmtId="212" formatCode="0.00"/>
+    <x:numFmt numFmtId="213" formatCode="0.000"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -120,7 +124,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -164,10 +168,10 @@
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -184,16 +188,34 @@
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="210" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -396,70 +418,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="13" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.95" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;人员&gt; &lt;补报期间&gt; 小红书补报明细</t>
+          <t>&lt;人员&gt; &lt;补报期间&gt; 小红书补报明细</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="21.95" customHeight="1">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">主期&lt;主期间&gt;｜&lt;补报说明&gt;</t>
+          <t>主期&lt;主期间&gt;｜&lt;补报说明&gt;</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="21.95" customHeight="1">
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">补报合计：&lt;金额&gt;元｜共&lt;笔数&gt;笔</t>
+          <t>补报实报合计：&lt;金额&gt;元｜费用合计：&lt;金额&gt;元｜共&lt;笔数&gt;笔</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="21.95" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">日期</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">支出明细</t>
+          <t>支出明细</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">单笔金额</t>
+          <t>单笔金额</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">费用组合计</t>
+          <t>费用组合计</t>
         </is>
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">备注 / 分类</t>
+          <t>备注 / 分类</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">备注</t>
+          <t>报销属性</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="21.95" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="31"/>
       <c r="B5" s="24"/>
       <c r="C5" s="32"/>
